--- a/tabtools/demo/demo_corrtab.xlsx
+++ b/tabtools/demo/demo_corrtab.xlsx
@@ -66,12 +66,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -80,33 +90,9 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -127,115 +113,73 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -257,92 +201,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="0"/>
@@ -370,87 +314,87 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -474,44 +418,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -525,10 +469,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -542,24 +486,24 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="0"/>

--- a/tabtools/demo/demo_corrtab.xlsx
+++ b/tabtools/demo/demo_corrtab.xlsx
@@ -103,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -113,6 +113,27 @@
     </border>
     <border/>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -121,7 +142,28 @@
     </border>
     <border>
       <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -130,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -142,13 +184,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="general" vertical="bottom" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -166,13 +223,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -201,19 +273,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -221,16 +293,16 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -238,16 +310,16 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -255,16 +327,16 @@
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -272,16 +344,16 @@
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -314,19 +386,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -334,16 +406,16 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -351,16 +423,16 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -368,16 +440,16 @@
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -385,16 +457,16 @@
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -418,92 +490,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="16" t="s">
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="A2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="24" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="0"/>

--- a/tabtools/demo/demo_corrtab.xlsx
+++ b/tabtools/demo/demo_corrtab.xlsx
@@ -50,13 +50,13 @@
     <t>Table 14. Spearman Rank Correlation Matrix</t>
   </si>
   <si>
-    <t>0.00 (0.616)</t>
-  </si>
-  <si>
-    <t>0.00 (0.807)</t>
-  </si>
-  <si>
-    <t>0.01 (0.450)</t>
+    <t>0.00 (0.62)</t>
+  </si>
+  <si>
+    <t>0.00 (0.81)</t>
+  </si>
+  <si>
+    <t>0.01 (0.45)</t>
   </si>
   <si>
     <t>Table 15. Pearson Correlation Matrix (Full)</t>
